--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8444b83b8e02447e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R38b5267670f04a42"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R38b5267670f04a42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5dfdd905529f4876"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5dfdd905529f4876"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd948a2c09d854ed4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd948a2c09d854ed4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc5e1582922174e8f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc5e1582922174e8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9be2e28e645a4d9a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9be2e28e645a4d9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra4220e4701f9492b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra4220e4701f9492b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbad516ad1dca4b8f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbad516ad1dca4b8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2b8c8b3ade0e4c60"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2b8c8b3ade0e4c60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc07c0d321c544342"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc07c0d321c544342"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R09618bd41dec43ff"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R09618bd41dec43ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R98b4e93ef18a4b6a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R98b4e93ef18a4b6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra5f5cba94d564e5c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra5f5cba94d564e5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf07e37f7613749a9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf07e37f7613749a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3eb1b0f0570d41d0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3eb1b0f0570d41d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb7947a257bd64c0e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb7947a257bd64c0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3f6b41e1cc334468"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3f6b41e1cc334468"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5ff6ee7c1d644e50"/>
   </x:sheets>
 </x:workbook>
 </file>
